--- a/Aplicaciones/Gestion/plantillas_excel/plantilla_matriculas.xlsx
+++ b/Aplicaciones/Gestion/plantillas_excel/plantilla_matriculas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UTC\8VO\TESIS\APLICACIÓN\Colegio\Aplicaciones\Gestion\plantillas_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFDC73EB-6852-4045-9C9A-741F1518129E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{085A3A7A-EC3D-489E-BA17-A4F9B3CE62A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PlantillaMatriculas" sheetId="1" r:id="rId1"/>
@@ -41,6 +41,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>OpenAI</author>
+    <author>PC</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
@@ -99,7 +100,21 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="E1" authorId="1" shapeId="0" xr:uid="{E8127487-3206-4EA2-9CC2-E738A2886E3E}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">OCTAVO NOVENO Y DECIMO NO APLICA
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -113,7 +128,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -127,7 +142,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -141,7 +156,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
@@ -155,7 +170,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
@@ -169,7 +184,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -188,7 +203,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>cedula_estudiante</t>
   </si>
@@ -308,13 +323,16 @@
   </si>
   <si>
     <t>DESERTOR</t>
+  </si>
+  <si>
+    <t>especialidad</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -363,6 +381,12 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -758,21 +782,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J500"/>
+  <dimension ref="A1:K500"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="5" max="5" width="33.5546875" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
     <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="11" max="11" width="22.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -786,25 +811,28 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="9"/>
       <c r="B2" s="10"/>
       <c r="C2" s="11"/>
@@ -816,7 +844,7 @@
       <c r="I2" s="8"/>
       <c r="J2" s="5"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -828,43 +856,43 @@
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
